--- a/design_issues/codescene/P4_JobApplication.xlsx
+++ b/design_issues/codescene/P4_JobApplication.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DIinAGP\DIinAGP\design_issues\codescene\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
